--- a/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistrationData.xlsx
+++ b/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistrationData.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{619D5151-7D64-48A1-804C-85B4DE14ED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kumar Saurav\git\repository4\testng-hybrid-selenium-framwork\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBE4E66-7EC3-4E75-9332-ACB4AAF308F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E66005CC-7BC7-4FDD-BFA8-AD6ABBF0C4FC}"/>
   </bookViews>
@@ -11,19 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -65,9 +60,6 @@
     <t>WesBengal</t>
   </si>
   <si>
-    <t>ChandanKr</t>
-  </si>
-  <si>
     <t>Chandan@2</t>
   </si>
   <si>
@@ -84,6 +76,9 @@
   </si>
   <si>
     <t>Confirm_Password</t>
+  </si>
+  <si>
+    <t>ChandanKrSah</t>
   </si>
 </sst>
 </file>
@@ -487,10 +482,10 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -502,10 +497,10 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -517,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -546,13 +541,13 @@
         <v>1245</v>
       </c>
       <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistrationData.xlsx
+++ b/testng-hybrid-selenium-framwork/src/test/resources/testdata/ParabankRegistrationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kumar Saurav\git\repository4\testng-hybrid-selenium-framwork\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBE4E66-7EC3-4E75-9332-ACB4AAF308F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10A41E9-00DF-4B9F-B488-844F0B56CD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E66005CC-7BC7-4FDD-BFA8-AD6ABBF0C4FC}"/>
   </bookViews>
@@ -78,7 +78,7 @@
     <t>Confirm_Password</t>
   </si>
   <si>
-    <t>ChandanKrSah</t>
+    <t>ChandanKr</t>
   </si>
 </sst>
 </file>
